--- a/backend/data/MAUFILE.xlsx
+++ b/backend/data/MAUFILE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\90503\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B41DA5-0A58-49F9-B997-2DA83F215F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1A7244-EFD9-4BB7-8E48-1B98C366CCE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="14" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Ghi chú</t>
   </si>
@@ -148,6 +145,9 @@
       </rPr>
       <t>(Cũ)</t>
     </r>
+  </si>
+  <si>
+    <t>Năm</t>
   </si>
 </sst>
 </file>
@@ -200,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -249,12 +249,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -268,9 +288,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -282,6 +299,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -564,86 +587,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FD9FE-BB40-4C98-B610-5D75AC179A73}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="1" customWidth="1"/>
-    <col min="5" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="19.85546875" style="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="6.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="19.85546875" style="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="2" t="s">
+    <row r="3" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -655,8 +684,9 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -668,8 +698,9 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -681,8 +712,9 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -694,8 +726,9 @@
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -707,8 +740,9 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -720,8 +754,9 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -733,8 +768,9 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -746,8 +782,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -759,8 +796,9 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -772,8 +810,9 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -785,8 +824,9 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -798,8 +838,9 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -811,8 +852,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -824,8 +866,9 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -837,8 +880,9 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -850,8 +894,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -863,8 +908,9 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -876,8 +922,9 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -889,8 +936,9 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -902,8 +950,9 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -915,8 +964,9 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -928,8 +978,9 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -941,8 +992,9 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -954,8 +1006,9 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -967,8 +1020,9 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -980,8 +1034,9 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -993,8 +1048,9 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1006,17 +1062,19 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A1:K1"/>
+  <mergeCells count="9">
     <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E2:I2"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
